--- a/Neptun.xlsx
+++ b/Neptun.xlsx
@@ -6529,7 +6529,7 @@
       </c>
       <c r="D216" s="5" t="inlineStr">
         <is>
-          <t>Earth from orbit at night with a green aurora shimmering over the mid-latitudes above southern Europe and the Mediterranean, far away from the poles, as if Earth's magnetic pole were moved, a surreal view that would never occur on Earth, 24mm lens, green aurora light. no illustration, no cartoon, no CGI glow, no neon, no fantasy.</t>
+          <t>Earth from orbit at night with a green aurora shimmering over the mid-latitudes above southern Europe and the Mediterranean, far away from the poles, as if Earth's magnetic pole were moved, 24mm lens, green aurora light. no illustration, no cartoon, no CGI glow, no neon, no fantasy.</t>
         </is>
       </c>
       <c r="E216" s="5" t="inlineStr">
